--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>
